--- a/docs/05-entregas/Flujo de Datos - Modulo 6 - UADEnet.xlsx
+++ b/docs/05-entregas/Flujo de Datos - Modulo 6 - UADEnet.xlsx
@@ -616,12 +616,12 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>{"titulo": "string", "descripcion": "string", "locacionId": "uuid", "cupoMaximo": "number (entero &gt; 0)", "fechaInicio": "datetime ISO 8601", "fechaFin": "datetime ISO 8601 (posterior a fechaInicio)", "esPago": "boolean", "precio": "number (entero &gt; 0) | null — obligatorio si esPago = true"} — responde 409 si la locación ya tiene un evento solapado en ese rango horario</t>
+          <t>{"titulo": "string", "descripcion": "string", "locacionId": "uuid", "cupoMaximo": "number (entero &gt; 0)", "fechaInicio": "datetime ISO 8601", "fechaFin": "datetime ISO 8601 (posterior a fechaInicio)", "esPago": "boolean", "categoriaPrecio": "general | especial | null — obligatorio si esPago = true, resuelto contra la tarifa vigente de Backoffice"} — responde 409 si la locación ya tiene un evento solapado en ese rango horario, o si la locación no está aptoEventos</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>{"titulo": "Charla: Arquitectura de Software", "descripcion": "Charla abierta sobre patrones de arquitectura.", "locacionId": "c1a4e8d2-7b36-4f90-8e52-1d0a9c3b6f47", "cupoMaximo": 80, "fechaInicio": "2026-10-15T18:00:00-03:00", "fechaFin": "2026-10-15T20:00:00-03:00", "esPago": false, "precio": null}</t>
+          <t>{"titulo": "Charla: Arquitectura de Software", "descripcion": "Charla abierta sobre patrones de arquitectura.", "locacionId": "c1a4e8d2-7b36-4f90-8e52-1d0a9c3b6f47", "cupoMaximo": 80, "fechaInicio": "2026-10-15T18:00:00-03:00", "fechaFin": "2026-10-15T20:00:00-03:00", "esPago": false, "categoriaPrecio": null}</t>
         </is>
       </c>
     </row>
@@ -648,12 +648,12 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>[{"id": "uuid", "titulo": "string", "descripcion": "string", "locacionId": "uuid", "cupoMaximo": "number", "fechaInicio": "datetime", "fechaFin": "datetime", "esPago": "boolean", "precio": "number | null", "creadoPor": "string (id de usuario en CORE)", "locacion": {"nombre": "string", "sede": "string"}, "inscriptos": "number", "disponibles": "number", "yaInscripto": "boolean"}] — ordenado por fechaInicio. desde/hasta son ISO 8601 opcionales y filtran por solapamiento con la ventana. Locación resuelta y cupo calculado para el calendario de los portales; yaInscripto se calcula contra el usuario del JWT</t>
+          <t>[{"id": "uuid", "titulo": "string", "descripcion": "string", "locacionId": "uuid", "cupoMaximo": "number", "fechaInicio": "datetime", "fechaFin": "datetime", "esPago": "boolean", "categoriaPrecio": "general | especial | null", "creadoPor": "string (id de usuario en CORE)", "locacion": {"nombre": "string", "sede": "string"}, "inscriptos": "number", "disponibles": "number", "yaInscripto": "boolean"}] — ordenado por fechaInicio. desde/hasta son ISO 8601 opcionales y filtran por solapamiento con la ventana. Locación resuelta y cupo calculado para el calendario de los portales; yaInscripto se calcula contra el usuario del JWT</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>[{"id": "9f2b7c14-3d5a-4e88-9a10-6c2d5e7f1b03", "titulo": "Charla: Arquitectura de Software", "descripcion": "Charla abierta sobre patrones de arquitectura.", "locacionId": "c1a4e8d2-7b36-4f90-8e52-1d0a9c3b6f47", "cupoMaximo": 80, "fechaInicio": "2026-10-15T18:00:00-03:00", "fechaFin": "2026-10-15T20:00:00-03:00", "esPago": false, "precio": null, "creadoPor": "u-10432", "locacion": {"nombre": "Aula Magna", "sede": "Monserrat"}, "inscriptos": 63, "disponibles": 17, "yaInscripto": false}]</t>
+          <t>[{"id": "9f2b7c14-3d5a-4e88-9a10-6c2d5e7f1b03", "titulo": "Charla: Arquitectura de Software", "descripcion": "Charla abierta sobre patrones de arquitectura.", "locacionId": "c1a4e8d2-7b36-4f90-8e52-1d0a9c3b6f47", "cupoMaximo": 80, "fechaInicio": "2026-10-15T18:00:00-03:00", "fechaFin": "2026-10-15T20:00:00-03:00", "esPago": false, "categoriaPrecio": null, "creadoPor": "u-10432", "locacion": {"nombre": "Aula Magna", "sede": "Monserrat"}, "inscriptos": 63, "disponibles": 17, "yaInscripto": false, "precio": null}]</t>
         </is>
       </c>
     </row>
@@ -712,12 +712,12 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>[{"id": "uuid", "nombre": "string", "sede": "string", "capacidad": "number"}] — catálogo propio, no se integra con Backoffice Administrativo (decidido, ver integraciones.md)</t>
+          <t>[{"id": "uuid", "nombre": "string", "sede": "string", "capacidad": "number", "aptoEventos": "boolean"}] — catálogo sincronizado desde Backoffice Administrativo (ver ADR 0013)</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>[{"id": "c1a4e8d2-7b36-4f90-8e52-1d0a9c3b6f47", "nombre": "Aula Magna", "sede": "Monserrat", "capacidad": 120}]</t>
+          <t>[{"id": "c1a4e8d2-7b36-4f90-8e52-1d0a9c3b6f47", "nombre": "Aula Magna", "sede": "Monserrat", "capacidad": 120, "aptoEventos": true}]</t>
         </is>
       </c>
     </row>
@@ -1042,20 +1042,68 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n"/>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Backoffice Administrativo</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Restful API</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>GET {BACKOFFICE_BASE_URL}/locaciones</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>[{"id": "uuid", "nombre": "string", "sede": "string", "capacidad": "number", "aptoEventos": "boolean"}] — catálogo de locaciones aptas para eventos, sincronizado periódicamente (ver ADR 0013)</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>[{"id": "c1a4e8d2-7b36-4f90-8e52-1d0a9c3b6f47", "nombre": "Aula Magna", "sede": "Monserrat", "capacidad": 120, "aptoEventos": true}]</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Backoffice Administrativo</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Restful API</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>GET {BACKOFFICE_BASE_URL}/tarifas/evento-inscripcion/{categoria}</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>{"categoria": "general | especial", "monto": "number (entero, en pesos)"} — tarifa vigente para esa categoría; se consulta al listar eventos y al confirmar cada inscripción paga</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>{"categoria": "especial", "monto": 12500}</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n"/>

--- a/docs/05-entregas/Flujo de Datos - Modulo 6 - UADEnet.xlsx
+++ b/docs/05-entregas/Flujo de Datos - Modulo 6 - UADEnet.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>[{"id": "uuid", "titulo": "string", "descripcion": "string", "locacionId": "uuid", "cupoMaximo": "number", "fechaInicio": "datetime", "fechaFin": "datetime", "esPago": "boolean", "categoriaPrecio": "general | especial | null", "creadoPor": "string (id de usuario en CORE)", "locacion": {"nombre": "string", "sede": "string"}, "inscriptos": "number", "disponibles": "number", "yaInscripto": "boolean"}] — ordenado por fechaInicio. desde/hasta son ISO 8601 opcionales y filtran por solapamiento con la ventana. Locación resuelta y cupo calculado para el calendario de los portales; yaInscripto se calcula contra el usuario del JWT</t>
+          <t>[{"id": "uuid", "titulo": "string", "descripcion": "string", "locacionId": "uuid", "cupoMaximo": "number", "fechaInicio": "datetime", "fechaFin": "datetime", "esPago": "boolean", "categoriaPrecio": "general | especial | null", "creadoPor": "string (id de usuario en CORE)", "locacion": {"nombre": "string", "sede": "string"}, "inscriptos": "number", "disponibles": "number", "yaInscripto": "boolean", "precio": "number | null — resuelto contra la tarifa vigente de Backoffice"}] — ordenado por fechaInicio. desde/hasta son ISO 8601 opcionales y filtran por solapamiento con la ventana. Locación resuelta y cupo calculado para el calendario de los portales; yaInscripto se calcula contra el usuario del JWT</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -680,12 +680,12 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>{"id": "uuid", "titulo": "string", "descripcion": "string", "locacionId": "uuid", "cupoMaximo": "number", "fechaInicio": "datetime", "fechaFin": "datetime", "esPago": "boolean", "precio": "number | null", "creadoPor": "string", "locacion": {"nombre": "string", "sede": "string"}, "inscriptos": "number", "disponibles": "number", "yaInscripto": "boolean"} — destino del link que enviamos en el recordatorio. Mismo objeto que el listado, sin array</t>
+          <t>{"id": "uuid", "titulo": "string", "descripcion": "string", "locacionId": "uuid", "cupoMaximo": "number", "fechaInicio": "datetime", "fechaFin": "datetime", "esPago": "boolean", "categoriaPrecio": "general | especial | null", "creadoPor": "string", "locacion": {"nombre": "string", "sede": "string"}, "inscriptos": "number", "disponibles": "number", "yaInscripto": "boolean", "precio": "number | null — resuelto contra la tarifa vigente de Backoffice"} — destino del link que enviamos en el recordatorio. Mismo objeto que el listado, sin array</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>{"id": "9f2b7c14-3d5a-4e88-9a10-6c2d5e7f1b03", "titulo": "Workshop de Testing", "descripcion": "Taller práctico de testing automatizado.", "locacionId": "c1a4e8d2-7b36-4f90-8e52-1d0a9c3b6f47", "cupoMaximo": 40, "fechaInicio": "2026-10-22T18:00:00-03:00", "fechaFin": "2026-10-22T21:00:00-03:00", "esPago": true, "precio": 4500, "creadoPor": "u-10432"}</t>
+          <t>{"id": "9f2b7c14-3d5a-4e88-9a10-6c2d5e7f1b03", "titulo": "Workshop de Testing", "descripcion": "Taller práctico de testing automatizado.", "locacionId": "c1a4e8d2-7b36-4f90-8e52-1d0a9c3b6f47", "cupoMaximo": 40, "fechaInicio": "2026-10-22T18:00:00-03:00", "fechaFin": "2026-10-22T21:00:00-03:00", "esPago": true, "categoriaPrecio": "especial", "creadoPor": "u-10432", "locacion": {"nombre": "Aula Magna", "sede": "Monserrat"}, "inscriptos": 63, "disponibles": 17, "yaInscripto": false, "precio": 4500}</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>[{"id": "uuid", "eventoId": "uuid", "usuarioId": "string", "fechaInscripcion": "datetime", "estado": "inscripto", "pagoConfirmado": "boolean"}] — devuelve las del usuario del JWT. La cancelación de inscripción no está en el alcance del TP, por eso estado tiene un único valor</t>
+          <t>[{"id": "uuid", "eventoId": "uuid", "usuarioId": "string", "fechaInscripcion": "datetime", "estado": "inscripto", "pagoConfirmado": "boolean", "montoCobrado": "number | null — congelado al confirmarse"}] — devuelve las del usuario del JWT. La cancelación de inscripción no está en el alcance del TP, por eso estado tiene un único valor</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>[{"id": "5e8d0b31-9c47-4a26-b18f-72e4c0d95a68", "eventoId": "9f2b7c14-3d5a-4e88-9a10-6c2d5e7f1b03", "usuarioId": "u-10432", "fechaInscripcion": "2026-09-30T14:22:10-03:00", "estado": "inscripto", "pagoConfirmado": true}]</t>
+          <t>[{"id": "5e8d0b31-9c47-4a26-b18f-72e4c0d95a68", "eventoId": "9f2b7c14-3d5a-4e88-9a10-6c2d5e7f1b03", "usuarioId": "u-10432", "fechaInscripcion": "2026-09-30T14:22:10-03:00", "estado": "inscripto", "pagoConfirmado": true, "montoCobrado": 12500}]</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>{"inscripcionId": "uuid", "metodo": "qr | codigo-en-sala | manual"} — los tres métodos son los que ya cubre el mock de /asistencia. Responde 409 si no existe una inscripción activa para esa inscripcionId</t>
+          <t>{"inscripcionId": "uuid", "metodo": "qr | manual"} — los dos métodos son los que ya cubre el mock de /asistencia (se descartó "código en sala" por ser el más débil en seguridad). Responde 409 si no existe una inscripción activa para esa inscripcionId</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>{"tipo": "evento.creado", "eventoId": "uuid", "titulo": "string", "locacionId": "uuid", "sede": "string", "cupoMaximo": "number", "fechaInicio": "datetime", "fechaFin": "datetime", "esPago": "boolean", "precio": "number | null", "emitidoEn": "datetime"} — alimenta la métrica de frecuencia de eventos</t>
+          <t>{"tipo": "evento.creado", "eventoId": "uuid", "titulo": "string", "locacionId": "uuid", "sede": "string", "cupoMaximo": "number", "fechaInicio": "datetime", "fechaFin": "datetime", "esPago": "boolean", "categoriaPrecio": "general | especial | null", "emitidoEn": "datetime"} — alimenta la métrica de frecuencia de eventos</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>{"tipo": "evento.creado", "eventoId": "9f2b7c14-3d5a-4e88-9a10-6c2d5e7f1b03", "titulo": "Workshop de Testing", "locacionId": "c1a4e8d2-7b36-4f90-8e52-1d0a9c3b6f47", "sede": "Monserrat", "cupoMaximo": 40, "fechaInicio": "2026-10-22T18:00:00-03:00", "fechaFin": "2026-10-22T21:00:00-03:00", "esPago": true, "precio": 4500, "emitidoEn": "2026-09-20T11:05:00-03:00"}</t>
+          <t>{"tipo": "evento.creado", "eventoId": "9f2b7c14-3d5a-4e88-9a10-6c2d5e7f1b03", "titulo": "Workshop de Testing", "locacionId": "c1a4e8d2-7b36-4f90-8e52-1d0a9c3b6f47", "sede": "Monserrat", "cupoMaximo": 40, "fechaInicio": "2026-10-22T18:00:00-03:00", "fechaFin": "2026-10-22T21:00:00-03:00", "esPago": true, "categoriaPrecio": "especial", "emitidoEn": "2026-09-20T11:05:00-03:00"}</t>
         </is>
       </c>
     </row>
@@ -1233,14 +1233,14 @@
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>Las estructuras publicadas acá son las que implementa nuestro módulo. Falta que CORE confirme el mecanismo de firma del JWT y el canal del recordatorio (cola vs REST), y que Analítica confirme los tres eventos — seguimiento en docs/02-arquitectura/integraciones.md.</t>
+          <t>Las estructuras publicadas acá son las que implementa nuestro módulo. Falta que CORE confirme el mecanismo de firma del JWT y el canal del recordatorio (cola vs REST), que Analítica confirme los tres eventos, y que Backoffice confirme el path del catálogo de locaciones y de la tarifa por categoría — seguimiento en docs/02-arquitectura/integraciones.md.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>Implementado en apps/api: todos los endpoints /api/v1 de esta planilla, con tests. El descuento de saldo de CORE está mockeado con saldo fijo; el recordatorio y los tres eventos hacia Analítica todavía no se emiten.</t>
+          <t>Implementado en apps/api: todos los endpoints /api/v1 de esta planilla, con tests. El descuento de saldo de CORE y la tarifa de inscripción de Backoffice están mockeados con valores fijos (saldo.service.ts y tarifas.service.ts); el recordatorio y los tres eventos hacia Analítica todavía no se emiten.</t>
         </is>
       </c>
     </row>

--- a/docs/05-entregas/Flujo de Datos - Modulo 6 - UADEnet.xlsx
+++ b/docs/05-entregas/Flujo de Datos - Modulo 6 - UADEnet.xlsx
@@ -1059,17 +1059,17 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>GET {BACKOFFICE_BASE_URL}/locaciones</t>
+          <t>GET /api/v1/backoffice/sedes/{sedeId}/espacios?aptoEventos=true</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>[{"id": "uuid", "nombre": "string", "sede": "string", "capacidad": "number", "aptoEventos": "boolean"}] — catálogo de locaciones aptas para eventos, sincronizado periódicamente (ver ADR 0013)</t>
+          <t>{"id": "uuid", "sedeId": "uuid", "codigo": "string", "nombre": "string", "tipo": "string (ej. SALA_EVENTOS)", "capacidad": "number", "aptoEventos": "boolean", "estado": "string (ej. ACTIVO)"} — se pide por sede, no hay listado global. La sede llega como sedeId (uuid), no como nombre: para la cartelera hay que resolverlo con GET /api/v1/backoffice/sedes (y cachearlo) o pedirle a Backoffice que lo embeba</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>[{"id": "c1a4e8d2-7b36-4f90-8e52-1d0a9c3b6f47", "nombre": "Aula Magna", "sede": "Monserrat", "capacidad": 120, "aptoEventos": true}]</t>
+          <t>{"id": "uuid", "sedeId": "uuid", "codigo": "A-305", "nombre": "Auditorio Principal", "tipo": "SALA_EVENTOS", "capacidad": 200, "aptoEventos": true, "estado": "ACTIVO"}</t>
         </is>
       </c>
     </row>
@@ -1091,17 +1091,17 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>GET {BACKOFFICE_BASE_URL}/tarifas/evento-inscripcion/{categoria}</t>
+          <t>GET /api/v1/backoffice/tarifas/vigente?concepto=EVENTO_INSCRIPCION_GENERAL|EVENTO_INSCRIPCION_ESPECIAL&amp;fecha=</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>{"categoria": "general | especial", "monto": "number (entero, en pesos)"} — tarifa vigente para esa categoría; se consulta al listar eventos y al confirmar cada inscripción paga</t>
+          <t>{"concepto": "EVENTO_INSCRIPCION_GENERAL | EVENTO_INSCRIPCION_ESPECIAL", "sede": "string | null", "ambitoResuelto": "string (ej. GLOBAL)", "monto": "number (decimal)", "moneda": "string (ej. ARS)", "unidad": "string (ej. MONTO_FIJO)", "vigencia": {"desde": "date", "hasta": "date | null"}, "tarifaId": "uuid"} — se resuelve al momento del cobro, no al crear el evento, para tomar siempre la versión vigente. 404 si no hay ninguna vigente para esa fecha; el fallback ante ese caso lo define este módulo</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>{"categoria": "especial", "monto": 12500}</t>
+          <t>{"concepto": "EVENTO_INSCRIPCION_GENERAL", "sede": null, "ambitoResuelto": "GLOBAL", "monto": 1800.00, "moneda": "ARS", "unidad": "MONTO_FIJO", "vigencia": {"desde": "2026-10-01", "hasta": null}, "tarifaId": "8f1e2d3c-4b5a-6789-0abc-def123456789"}</t>
         </is>
       </c>
     </row>
@@ -1233,14 +1233,14 @@
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>Las estructuras publicadas acá son las que implementa nuestro módulo. Falta que CORE confirme el mecanismo de firma del JWT y el canal del recordatorio (cola vs REST), que Analítica confirme los tres eventos, y que Backoffice confirme el path del catálogo de locaciones y de la tarifa por categoría — seguimiento en docs/02-arquitectura/integraciones.md.</t>
+          <t>Las estructuras publicadas acá son las que implementa nuestro módulo. Falta que CORE confirme el mecanismo de firma del JWT y el canal del recordatorio (cola vs REST), y que Analítica confirme los tres eventos — seguimiento en docs/02-arquitectura/integraciones.md. Backoffice ya confirmó path y shape de espacios y tarifa vigente; queda pendiente de nuestro lado definir cómo resolvemos el nombre de sede a partir de sedeId, y el fallback ante un 404 de tarifa vigente.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>Implementado en apps/api: todos los endpoints /api/v1 de esta planilla, con tests. El descuento de saldo de CORE y la tarifa de inscripción de Backoffice están mockeados con valores fijos (saldo.service.ts y tarifas.service.ts); el recordatorio y los tres eventos hacia Analítica todavía no se emiten.</t>
+          <t>Implementado en apps/api: todos los endpoints /api/v1 de esta planilla, con tests. El descuento de saldo de CORE está mockeado con saldo fijo (saldo.service.ts); la tarifa de inscripción de Backoffice está mockeada con valores fijos en tarifas.service.ts pero todavía no refleja el shape real que confirmó Backoffice (concepto, vigencia, tarifaId) — pendiente de actualizar cuando se implemente la integración real; el recordatorio y los tres eventos hacia Analítica todavía no se emiten.</t>
         </is>
       </c>
     </row>
